--- a/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X134"/>
+  <dimension ref="A1:X132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,7 +926,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688857632794327</t>
+          <t>1688857885896779</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -941,17 +941,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -963,11 +963,11 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -980,12 +980,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688854397789505</t>
+          <t>1688858265888031</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1129,37 +1129,37 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688857041843101</t>
+          <t>1688855925819373</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -1173,22 +1173,22 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688854957840124</t>
+          <t>1688857545861192</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1268,12 +1268,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1282,17 +1277,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1322,7 +1317,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1332,32 +1327,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688856602829916</t>
+          <t>1688858249747099</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1376,22 +1371,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1431,32 +1426,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688856840767059</t>
+          <t>1688857632794447</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>张熙盈</t>
+          <t>田梦洁</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zhangxiying</t>
+          <t>tianmengjie</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1475,17 +1470,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>张熙盈</t>
+          <t>田梦洁</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>zhangxiying</t>
+          <t>tianmengjie</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1530,7 +1525,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688854902879055</t>
+          <t>1688854745905297</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1540,22 +1535,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1579,12 +1574,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1629,32 +1624,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688858213891390</t>
+          <t>1688856187931317</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1666,24 +1661,29 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14</t>
+        </is>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688858311666546</t>
+          <t>1688855990601283</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688856520846151</t>
+          <t>1688855102831881</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1837,22 +1837,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>冯光远</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>fengguangyuan</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1864,7 +1864,12 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>9,10,11</t>
+        </is>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1876,12 +1881,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>冯光远</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>fengguangyuan</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1916,7 +1921,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1926,37 +1931,37 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688857258634877</t>
+          <t>1688857545861192</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1970,22 +1975,22 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2025,32 +2030,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688857632794355</t>
+          <t>1688857632794260</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>谢宇龙</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>xieyulong</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2065,26 +2070,21 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>谢宇龙</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>xieyulong</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2129,32 +2129,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688857632794346</t>
+          <t>1688856168895940</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>赵莉</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>zhaoli</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2166,29 +2166,24 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>8,9,10</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>赵莉</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>zhaoli</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2223,7 +2218,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2233,66 +2228,76 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688857545861170</t>
+          <t>1688857632794355</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>谢宇龙</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>xieyulong</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14</t>
+        </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>谢宇龙</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>xieyulong</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2332,32 +2337,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688857794712832</t>
+          <t>1688856504741421</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>王东发</t>
+          <t>刘若凌</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>wangdongfa</t>
+          <t>liuruoling</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2376,17 +2381,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>王东发</t>
+          <t>刘若凌</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>wangdongfa</t>
+          <t>liuruoling</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2431,32 +2436,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688857541861019</t>
+          <t>1688856168896142</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>田名扬</t>
+          <t>任灿</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>tianmingyang01</t>
+          <t>rencan</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2475,17 +2480,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>田名扬</t>
+          <t>任灿</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>tianmingyang01</t>
+          <t>rencan</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2530,32 +2535,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688857014907414</t>
+          <t>1688856145888031</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>朱浩楠</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>zhuhaonan</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2567,24 +2572,29 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>8,9,10,11</t>
+        </is>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>朱浩楠</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>zhuhaonan</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2629,32 +2639,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688855034811328</t>
+          <t>1688857859856215</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2673,17 +2683,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2718,7 +2728,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2728,7 +2738,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688858397734047</t>
+          <t>1688858067856980</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2738,22 +2748,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2777,17 +2787,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2817,7 +2827,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2827,32 +2837,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688857545861170</t>
+          <t>1688857471687073</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2871,22 +2881,22 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2916,7 +2926,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2926,71 +2936,66 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688854745905297</t>
+          <t>1688857041843101</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3030,32 +3035,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688857632794436</t>
+          <t>1688856504741288</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>李孜涵</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>lizihan02</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3074,17 +3079,17 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>李孜涵</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>lizihan02</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3129,7 +3134,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688857472723498</t>
+          <t>1688856187931234</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3139,22 +3144,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3166,7 +3171,12 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
@@ -3178,12 +3188,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3228,32 +3238,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688858213891414</t>
+          <t>1688854735807615</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>侯鑫冉</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>houxinran01</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3265,29 +3275,24 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>侯鑫冉</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>houxinran01</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3332,32 +3337,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688856722866488</t>
+          <t>1688854970874060</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3376,17 +3381,17 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3431,7 +3436,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688854735807615</t>
+          <t>1688856840767059</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3441,22 +3446,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>张熙盈</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>zhangxiying</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3480,12 +3485,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>张熙盈</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>zhangxiying</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3530,7 +3535,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688857545861192</t>
+          <t>1688857041843101</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3545,22 +3550,22 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -3579,12 +3584,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3629,32 +3634,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688856504741421</t>
+          <t>1688858083589918</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>刘若凌</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>liuruoling</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3673,17 +3678,17 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>刘若凌</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>liuruoling</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3728,32 +3733,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688858249747099</t>
+          <t>1688857632794423</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3772,17 +3777,17 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3827,7 +3832,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688854717819422</t>
+          <t>1688855319787208</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3842,17 +3847,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>刘旭琳</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>liuxulin</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3876,12 +3881,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>刘旭琳</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>liuxulin</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3926,32 +3931,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688857325680107</t>
+          <t>1688856520846151</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>武亚伟</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>wuyawei</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3963,24 +3968,29 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10,11,12,13</t>
+        </is>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>武亚伟</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>wuyawei</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4015,7 +4025,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4025,32 +4035,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688857545861192</t>
+          <t>1688857632794327</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4062,29 +4072,34 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4124,32 +4139,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688856504741446</t>
+          <t>1688854957840149</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>吴思琪</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>wusiqi01</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4168,17 +4183,17 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>吴思琪</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>wusiqi01</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4223,32 +4238,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688856168895775</t>
+          <t>1688857258634877</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4267,17 +4282,17 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4322,32 +4337,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688854717819385</t>
+          <t>1688857472723498</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>刘逸飞</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>liuyifei</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4362,26 +4377,21 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>刘逸飞</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>liuyifei</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4416,7 +4426,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4426,7 +4436,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688857951732153</t>
+          <t>1688856504741311</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4436,27 +4446,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -4475,17 +4485,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -4525,32 +4535,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688858083589918</t>
+          <t>1688857749872491</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4569,17 +4579,17 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4624,7 +4634,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688857749872444</t>
+          <t>1688855493781803</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4634,22 +4644,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>何佳泽</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>hejiaze01</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4673,12 +4683,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>何佳泽</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>hejiaze01</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4723,32 +4733,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688857471687073</t>
+          <t>1688854957840124</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4767,17 +4777,17 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4812,7 +4822,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4822,32 +4832,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688855618877748</t>
+          <t>1688856602829916</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>杨梦涛</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>yangmengtao</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4866,22 +4876,22 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>杨梦涛</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>yangmengtao</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -4921,32 +4931,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688858356858328</t>
+          <t>1688855593870539</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>申萌</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>shenmeng01</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4958,24 +4968,29 @@
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>11,12,13</t>
+        </is>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>申萌</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>shenmeng01</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5020,32 +5035,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688857169652360</t>
+          <t>1688858356858328</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>新兵营烁-李智慧</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>张欣宇</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zhangxinyu</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5064,17 +5079,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>张欣宇</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>zhangxinyu</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -5119,7 +5134,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688856504741288</t>
+          <t>1688858311666546</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5129,22 +5144,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5156,12 +5171,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
@@ -5173,12 +5183,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5223,7 +5233,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688857632794412</t>
+          <t>1688858248913068</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5233,22 +5243,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>杨子澳</t>
+          <t>高科</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>yangziao</t>
+          <t>gaoke02</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5260,12 +5270,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -5277,12 +5282,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>杨子澳</t>
+          <t>高科</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>yangziao</t>
+          <t>gaoke02</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5327,32 +5332,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688857632794423</t>
+          <t>1688857014907414</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5371,17 +5376,17 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5426,32 +5431,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688856168896142</t>
+          <t>1688857749872459</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>任灿</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>rencan</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5470,17 +5475,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>任灿</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>rencan</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5515,7 +5520,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5525,32 +5530,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688858067856857</t>
+          <t>1688857632794403</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>刘佳伟</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>liujiawei</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5562,29 +5567,34 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>刘佳伟</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>liujiawei</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -5614,7 +5624,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5624,37 +5634,37 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688854397788387</t>
+          <t>1688854957840073</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -5668,22 +5678,22 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -5713,7 +5723,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5723,37 +5733,37 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688858173853397</t>
+          <t>1688855071729227</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -5767,22 +5777,22 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -5822,32 +5832,32 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688857632794260</t>
+          <t>1688855618814007</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5866,17 +5876,17 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5921,32 +5931,32 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688854346786884</t>
+          <t>1688855946578976</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>王晓慧</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>wangxiaohui</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5965,17 +5975,17 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>王晓慧</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>wangxiaohui</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -6020,32 +6030,32 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688856804923400</t>
+          <t>1688855925819350</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>李作鹏</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>lizuopeng</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -6064,17 +6074,17 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>李作鹏</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>lizuopeng</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -6119,7 +6129,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688854700793351</t>
+          <t>1688857257880743</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6129,22 +6139,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6168,12 +6178,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6208,7 +6218,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6218,37 +6228,37 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688857632794362</t>
+          <t>1688854397789505</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -6262,22 +6272,22 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -6317,7 +6327,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688857104713888</t>
+          <t>1688858076923296</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6332,17 +6342,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6366,12 +6376,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6416,32 +6426,32 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688854957840137</t>
+          <t>1688854957840114</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>李金儒</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>lijinru02</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6450,42 +6460,27 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>李金儒</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>lijinru02</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6530,32 +6525,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688857484684695</t>
+          <t>1688856187931241</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>刘清杨</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>liuqingyang</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6567,29 +6562,24 @@
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>刘清杨</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>liuqingyang</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6634,7 +6624,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688858265888031</t>
+          <t>1688854397789505</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6649,22 +6639,22 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -6683,12 +6673,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6733,7 +6723,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688856602829916</t>
+          <t>1688854397788387</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6748,22 +6738,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -6782,12 +6772,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6832,32 +6822,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688856168895797</t>
+          <t>1688856961861713</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6869,29 +6859,29 @@
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q61" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6936,32 +6926,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688855073726560</t>
+          <t>1688858397734047</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6976,26 +6966,21 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7040,32 +7025,32 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688856961861713</t>
+          <t>1688855073726560</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7077,29 +7062,24 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -7134,7 +7114,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7144,66 +7124,71 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688856804923405</t>
+          <t>1688858067856857</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -7243,32 +7228,32 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688857632794403</t>
+          <t>1688856955546120</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>刘佳伟</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>liujiawei</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7280,29 +7265,24 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>刘佳伟</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>liujiawei</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7347,7 +7327,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688856187931241</t>
+          <t>1688854346786888</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -7362,17 +7342,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>刘清杨</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>liuqingyang</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7384,7 +7364,12 @@
         <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q66" t="n">
         <v>1</v>
@@ -7396,12 +7381,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>刘清杨</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>liuqingyang</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7446,32 +7431,32 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688856145888031</t>
+          <t>1688857484684695</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>朱浩楠</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zhuhaonan</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7483,11 +7468,11 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>14,15,17,18</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="Q67" t="n">
@@ -7495,17 +7480,17 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>朱浩楠</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>zhuhaonan</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7550,32 +7535,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688854745834995</t>
+          <t>1688857531803728</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>黄瑞倩</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>huangruiqian</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7594,17 +7579,17 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>黄瑞倩</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>huangruiqian</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7649,32 +7634,32 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688854689492851</t>
+          <t>1688855593870536</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>王立进</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>wanglijin01</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7693,17 +7678,17 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>王立进</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>wanglijin01</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7748,32 +7733,32 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688855713584928</t>
+          <t>1688857382830184</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>姚明</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>yaoming01</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7792,17 +7777,17 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>姚明</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>yaoming01</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7847,32 +7832,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688855319787208</t>
+          <t>1688855618877748</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>杨梦涛</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>yangmengtao</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7884,24 +7869,29 @@
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>杨梦涛</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>yangmengtao</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7946,32 +7936,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688854617822809</t>
+          <t>1688854745834995</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>范嘉威</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fanjiawei</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7990,17 +7980,17 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>范嘉威</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>fanjiawei</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -8045,32 +8035,32 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688856387799602</t>
+          <t>1688857794712832</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>武祺祥</t>
+          <t>王东发</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>wuqixiang</t>
+          <t>wangdongfa</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -8079,42 +8069,42 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>武祺祥</t>
+          <t>王东发</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>wuqixiang</t>
+          <t>wangdongfa</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -8159,32 +8149,32 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688854957840073</t>
+          <t>1688857632794248</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -8203,17 +8193,17 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -8258,32 +8248,32 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688854717819330</t>
+          <t>1688858213891390</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8302,17 +8292,17 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8357,32 +8347,32 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688856504741335</t>
+          <t>1688856387799602</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>武祺祥</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>wuqixiang</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8391,27 +8381,42 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>武祺祥</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>wuqixiang</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -8456,32 +8461,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688855618814007</t>
+          <t>1688854717819330</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8500,17 +8505,17 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -8555,32 +8560,32 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688858356858343</t>
+          <t>1688856504741335</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8592,29 +8597,24 @@
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688858079797450</t>
+          <t>1688854397788387</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8674,22 +8674,22 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>赵园园</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>zhaoyuanyuan</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M79" t="n">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>赵园园</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>zhaoyuanyuan</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688856187931317</t>
+          <t>1688856187931330</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -8773,17 +8773,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8795,7 +8795,12 @@
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
@@ -8807,12 +8812,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8857,7 +8862,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688856840766973,1688857529572218</t>
+          <t>1688858356858333</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8867,22 +8872,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8906,12 +8911,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8956,32 +8961,32 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1688855925819373</t>
+          <t>1688857632794455</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>翟心惠</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>zhaixinhui</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -9000,17 +9005,17 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>翟心惠</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>zhaixinhui</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -9055,32 +9060,32 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1688854346786588</t>
+          <t>1688857632794412</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>杨子澳</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>yangziao</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -9095,26 +9100,21 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>杨子澳</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>yangziao</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1688854957840114</t>
+          <t>1688857545861170</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -9169,27 +9169,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -9208,17 +9208,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1688854397789505</t>
+          <t>1688857632794436</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -9268,22 +9268,22 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>李孜涵</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>lizihan02</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9307,17 +9307,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>李孜涵</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>lizihan02</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1688857632794455</t>
+          <t>1688857541861019</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -9372,17 +9372,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>翟心惠</t>
+          <t>田名扬</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>zhaixinhui</t>
+          <t>tianmingyang01</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>翟心惠</t>
+          <t>田名扬</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>zhaixinhui</t>
+          <t>tianmingyang01</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1688858234639755</t>
+          <t>1688856520845931</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9471,17 +9471,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1688855946578976</t>
+          <t>1688854346786884</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>王晓慧</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>wangxiaohui</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9604,17 +9604,17 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>王晓慧</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>wangxiaohui</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1688855493781803</t>
+          <t>1688856722866488</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9669,22 +9669,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>何佳泽</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>hejiaze01</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9699,12 +9699,7 @@
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -9713,12 +9708,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>何佳泽</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>hejiaze01</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -9763,32 +9758,32 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1688857257880743</t>
+          <t>1688857118654801</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9807,17 +9802,17 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -9862,32 +9857,32 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1688854970874060</t>
+          <t>1688858234639755</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9899,24 +9894,29 @@
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q91" t="n">
         <v>1</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9961,32 +9961,32 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1688857632794447</t>
+          <t>1688854957840137</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>田梦洁</t>
+          <t>李金儒</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>tianmengjie</t>
+          <t>lijinru02</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9995,27 +9995,42 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="Q92" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>田梦洁</t>
+          <t>李金儒</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>tianmengjie</t>
+          <t>lijinru02</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -10050,7 +10065,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10060,7 +10075,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1688858265888031</t>
+          <t>1688854717819422</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -10070,22 +10085,22 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -10109,17 +10124,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -10159,7 +10174,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1688857632794248</t>
+          <t>1688857525693645</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -10174,17 +10189,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -10208,12 +10223,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -10258,32 +10273,32 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1688857587778504</t>
+          <t>1688854700793351</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -10298,26 +10313,21 @@
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -10362,32 +10372,32 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1688857525693645</t>
+          <t>1688857749872444</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -10406,17 +10416,17 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -10461,32 +10471,32 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1688858356858333</t>
+          <t>1688854941520680</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>刘帅</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>liushuai05</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10505,17 +10515,17 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>刘帅</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>liushuai05</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -10560,7 +10570,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1688858076923296</t>
+          <t>1688854902879055</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10575,17 +10585,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10594,28 +10604,13 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -10624,12 +10619,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -10674,32 +10669,32 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1688857950813447</t>
+          <t>1688857632794346</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>赵莉</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>zhaoli</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10711,29 +10706,29 @@
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="Q99" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>赵莉</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>zhaoli</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -10778,32 +10773,32 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1688854957840149</t>
+          <t>1688856187931267</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>吴思琪</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>wusiqi01</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10815,24 +10810,29 @@
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11,12,13</t>
+        </is>
       </c>
       <c r="Q100" t="n">
         <v>1</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>吴思琪</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>wusiqi01</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1688858173853397</t>
+          <t>1688855034811328</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10887,22 +10887,22 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10926,17 +10926,17 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -10976,32 +10976,32 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1688856168895940</t>
+          <t>1688857169652360</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>张欣宇</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>zhangxinyu</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -11020,17 +11020,17 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>张欣宇</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>zhangxinyu</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1688857041843101</t>
+          <t>1688854717819385</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>刘逸飞</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>liuyifei</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -11119,22 +11119,22 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>刘逸飞</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>liuyifei</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -11174,32 +11174,32 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1688856504741311</t>
+          <t>1688856504741446</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -11218,17 +11218,17 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -11273,32 +11273,32 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1688856504741386</t>
+          <t>1688855713584928</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>姚明</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>yaoming01</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -11317,17 +11317,17 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>姚明</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>yaoming01</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -11372,32 +11372,32 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1688856520845931</t>
+          <t>1688858356858343</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -11409,29 +11409,24 @@
         <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q106" t="n">
         <v>1</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -11466,7 +11461,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11476,32 +11471,32 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1688856187931330</t>
+          <t>1688858067856857</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -11513,29 +11508,34 @@
         <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q107" t="n">
         <v>1</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -11575,32 +11575,32 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1688857382830184</t>
+          <t>1688856804923400</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11674,32 +11674,32 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1688857951732153</t>
+          <t>1688857983840940</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -11718,22 +11718,22 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -11773,32 +11773,32 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1688858248913068</t>
+          <t>1688856168895797</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>高科</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>gaoke02</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -11817,17 +11817,17 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>高科</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>gaoke02</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11872,71 +11872,66 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1688857885896779</t>
+          <t>1688856602829916</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M111" t="n">
         <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q111" t="n">
         <v>1</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -11976,32 +11971,32 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1688855990601283</t>
+          <t>1688854346786588</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -12013,24 +12008,29 @@
         <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>10,11,12,13</t>
+        </is>
       </c>
       <c r="Q112" t="n">
         <v>1</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1688856722866484</t>
+          <t>1688858079797450</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>赵园园</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>zhaoyuanyuan</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -12119,22 +12119,22 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>赵园园</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>zhaoyuanyuan</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
@@ -12174,32 +12174,32 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1688854941520680</t>
+          <t>1688856840766973,1688857529572218</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>刘帅</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>liushuai05</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -12218,17 +12218,17 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>刘帅</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>liushuai05</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -12273,32 +12273,32 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1688856187931234</t>
+          <t>1688858213891414</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>侯鑫冉</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>houxinran01</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -12310,11 +12310,11 @@
         <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="Q115" t="n">
@@ -12322,17 +12322,17 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>侯鑫冉</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>houxinran01</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -12377,32 +12377,32 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1688855102831881</t>
+          <t>1688857587778504</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>冯光远</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>fengguangyuan</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -12414,29 +12414,24 @@
         <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>冯光远</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>fengguangyuan</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -12481,7 +12476,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1688854397788387</t>
+          <t>1688858173853397</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -12496,22 +12491,22 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -12530,12 +12525,12 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -12580,32 +12575,32 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1688855593870536</t>
+          <t>1688857950813447</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -12624,17 +12619,17 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -12679,32 +12674,32 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1688855593870539</t>
+          <t>1688857325680107</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>申萌</t>
+          <t>武亚伟</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>shenmeng01</t>
+          <t>wuyawei</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -12716,29 +12711,24 @@
         <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q119" t="n">
         <v>1</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>申萌</t>
+          <t>武亚伟</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>shenmeng01</t>
+          <t>wuyawei</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -12783,32 +12773,32 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1688857859856215</t>
+          <t>1688854617822809</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>范嘉威</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>fanjiawei</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -12827,17 +12817,17 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>范嘉威</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>fanjiawei</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -12882,32 +12872,32 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1688855071729227</t>
+          <t>1688857632794362</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -12926,17 +12916,17 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -12981,7 +12971,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1688856955546120</t>
+          <t>1688856168895775</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -12991,22 +12981,22 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -13030,12 +13020,12 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -13080,32 +13070,32 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1688854346786888</t>
+          <t>1688858188639828</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -13117,29 +13107,24 @@
         <v>1</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q123" t="n">
         <v>1</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -13174,7 +13159,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -13184,32 +13169,32 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1688855968871592,1688857401525365</t>
+          <t>1688858173853397</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -13221,34 +13206,29 @@
         <v>1</v>
       </c>
       <c r="O124" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q124" t="n">
         <v>1</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
@@ -13288,32 +13268,32 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1688857983840940</t>
+          <t>1688856504741386</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -13332,17 +13312,17 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -13387,32 +13367,32 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1688855925819350</t>
+          <t>1688857401525365,1688855968871592</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>李作鹏</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>lizuopeng</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -13431,17 +13411,17 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>李作鹏</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>lizuopeng</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -13476,7 +13456,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -13486,32 +13466,32 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1688858188639828</t>
+          <t>1688858265888031</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -13523,34 +13503,29 @@
         <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q127" t="n">
         <v>1</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -13590,32 +13565,32 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1688857749872459</t>
+          <t>1688856804923405</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -13634,17 +13609,17 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -13689,32 +13664,32 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1688857531803728</t>
+          <t>1688857104713888</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>黄瑞倩</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>huangruiqian</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -13733,17 +13708,17 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>黄瑞倩</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>huangruiqian</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -13788,32 +13763,32 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1688857118654801</t>
+          <t>1688856722866484</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -13832,17 +13807,17 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -13887,32 +13862,32 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1688856187931267</t>
+          <t>1688854689492851</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>王立进</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>wanglijin01</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -13924,29 +13899,24 @@
         <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>王立进</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>wanglijin01</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -13991,7 +13961,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1688858067856980</t>
+          <t>1688857545861170</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -14006,17 +13976,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -14040,12 +14010,12 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -14059,204 +14029,6 @@
         </is>
       </c>
       <c r="X132" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>1688857749872491</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>劲揽山河-刘劲松</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>王如梦</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>wangrumeng</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M133" t="n">
-        <v>1</v>
-      </c>
-      <c r="O133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>1</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>王如梦</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>wangrumeng</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>1688858067856857</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>紫翼飞腾-商紫强</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>周庆有</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>zhouqingyou</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>0元</t>
-        </is>
-      </c>
-      <c r="M134" t="n">
-        <v>1</v>
-      </c>
-      <c r="O134" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>1</v>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>周庆有</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>zhouqingyou</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
         <is>
           <t>石家庄高短</t>
         </is>
@@ -14370,10 +14142,10 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
@@ -14402,16 +14174,16 @@
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="5">
@@ -14429,16 +14201,16 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="6">
@@ -14461,10 +14233,10 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G6" t="n">
         <v>9</v>
@@ -14499,10 +14271,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -14525,16 +14297,16 @@
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>0.75</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -14552,16 +14324,16 @@
         <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="G9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="10">
@@ -14616,10 +14388,10 @@
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>8</v>
@@ -14648,16 +14420,16 @@
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -14675,16 +14447,16 @@
         <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
     <row r="14">
@@ -14707,10 +14479,10 @@
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>11</v>
@@ -14739,10 +14511,10 @@
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>9</v>
@@ -14771,16 +14543,16 @@
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="17">
@@ -14830,16 +14602,16 @@
         <v>44</v>
       </c>
       <c r="E18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9318181818181818</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.8636363636363636</v>
       </c>
     </row>
     <row r="19">
@@ -14857,10 +14629,10 @@
         <v>123</v>
       </c>
       <c r="E19" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9024390243902439</v>
+        <v>0.967479674796748</v>
       </c>
       <c r="G19" t="n">
         <v>99</v>
@@ -14896,7 +14668,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄高短）-9月9日</t>
+          <t>企微风灵全天在线情况通晒（石家庄高短）-9月10日</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
@@ -15011,10 +14783,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>5</v>
@@ -15035,16 +14807,16 @@
         <v>9</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="7">
@@ -15059,16 +14831,16 @@
         <v>20</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="8">
@@ -15087,10 +14859,10 @@
         <v>13</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>9</v>
@@ -15117,10 +14889,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -15135,16 +14907,16 @@
         <v>12</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>0.75</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -15159,16 +14931,16 @@
         <v>35</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="12">
@@ -15211,10 +14983,10 @@
         <v>8</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>8</v>
@@ -15235,16 +15007,16 @@
         <v>8</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -15259,16 +15031,16 @@
         <v>24</v>
       </c>
       <c r="E15" s="23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
     <row r="16">
@@ -15287,10 +15059,10 @@
         <v>11</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G16" s="17" t="n">
         <v>11</v>
@@ -15311,10 +15083,10 @@
         <v>10</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>9</v>
@@ -15335,16 +15107,16 @@
         <v>11</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="19">
@@ -15383,16 +15155,16 @@
         <v>44</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>0.9318181818181818</v>
+        <v>1</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.8636363636363636</v>
       </c>
     </row>
     <row r="21">
@@ -15411,10 +15183,10 @@
         <v>123</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>0.9024390243902439</v>
+        <v>0.967479674796748</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>99</v>
